--- a/эк обоснование.xlsx
+++ b/эк обоснование.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pavel\Desktop\diploma2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF4AA28-280B-4D20-8B9C-85D776AD18FE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8961F7A4-6081-4B1D-A91E-E241C1B95009}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,6 +131,13 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -152,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -178,10 +185,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -718,7 +722,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{6BE8D5A2-0BDF-4116-941E-726492381CCC}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                      <a:rPr lang="ru-RU"/>
                       <a:pPr/>
                       <a:t>[ДИАПАЗОН ЯЧЕЕК]</a:t>
                     </a:fld>
@@ -736,7 +740,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -752,7 +755,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{C8DFE6F1-1BC0-43D9-8396-553A81C49173}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                      <a:rPr lang="ru-RU"/>
                       <a:pPr/>
                       <a:t>[ДИАПАЗОН ЯЧЕЕК]</a:t>
                     </a:fld>
@@ -770,7 +773,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -858,10 +860,10 @@
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>3855</c:v>
+                  <c:v>2278.23</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1927</c:v>
+                  <c:v>1230</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -873,10 +875,10 @@
                 <c15:dlblRangeCache>
                   <c:ptCount val="2"/>
                   <c:pt idx="0">
-                    <c:v>3855 Р</c:v>
+                    <c:v>2278,23 Р</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>1927 Р</c:v>
+                    <c:v>1230 Р</c:v>
                   </c:pt>
                 </c15:dlblRangeCache>
               </c15:datalabelsRange>
@@ -2469,7 +2471,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="57.6" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>3</v>
       </c>
@@ -2484,11 +2486,11 @@
         <v>10</v>
       </c>
       <c r="G2" s="9">
-        <v>3855</v>
+        <v>2278.23</v>
       </c>
       <c r="H2" s="4" t="str">
         <f>G2&amp;" Р"</f>
-        <v>3855 Р</v>
+        <v>2278,23 Р</v>
       </c>
       <c r="O2" s="4" t="s">
         <v>15</v>
@@ -2497,7 +2499,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="57.6" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>4</v>
       </c>
@@ -2511,12 +2513,12 @@
       <c r="F3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="10">
-        <v>1927</v>
+      <c r="G3" s="9">
+        <v>1230</v>
       </c>
       <c r="H3" s="4" t="str">
         <f>G3&amp;" Р"</f>
-        <v>1927 Р</v>
+        <v>1230 Р</v>
       </c>
       <c r="O3" s="4" t="s">
         <v>16</v>
